--- a/Feuilles/Phoenix.xlsx
+++ b/Feuilles/Phoenix.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanaismusic/Documents/CLIC/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanaismusic/Documents/CLIC/Feuilles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96938D40-DEA3-4B49-B7A9-4117F4D04BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2CEEEE-5336-544F-8FEF-A39B5EA4DF01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5740" yWindow="3280" windowWidth="28040" windowHeight="17440" xr2:uid="{2F1647A4-8C84-E14B-83BA-CB692A19D8A6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>MES</t>
   </si>
@@ -86,7 +86,10 @@
     <t>REFRAIN 5</t>
   </si>
   <si>
-    <t>REFRAIN  4</t>
+    <t>LOOP</t>
+  </si>
+  <si>
+    <t>REFRAIN 4</t>
   </si>
 </sst>
 </file>
@@ -458,10 +461,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85B34C31-2D9C-7940-9F39-E67ACD52E89F}">
-  <dimension ref="A1:D224"/>
+  <dimension ref="A1:E224"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -474,8 +477,11 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -489,7 +495,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -500,7 +506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -511,7 +517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -522,7 +528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -533,7 +539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -544,7 +550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -555,7 +561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -566,7 +572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -580,7 +586,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -591,7 +597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -602,7 +608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -613,7 +619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -624,7 +630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -635,7 +641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1346,7 +1352,7 @@
         <v>0</v>
       </c>
       <c r="D78" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">

--- a/Feuilles/Phoenix.xlsx
+++ b/Feuilles/Phoenix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanaismusic/Documents/CLIC/Feuilles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2CEEEE-5336-544F-8FEF-A39B5EA4DF01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CADA8AB-1324-E94D-AB1E-4DEB18B6EBDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5740" yWindow="3280" windowWidth="28040" windowHeight="17440" xr2:uid="{2F1647A4-8C84-E14B-83BA-CB692A19D8A6}"/>
   </bookViews>
@@ -96,10 +96,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -125,8 +132,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1013,7 +1021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1024,7 +1032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1037,8 +1045,11 @@
       <c r="D50" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1049,7 +1060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>51</v>
       </c>
@@ -1060,7 +1071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>52</v>
       </c>
@@ -1071,7 +1082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>53</v>
       </c>
@@ -1082,7 +1093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>54</v>
       </c>
@@ -1093,7 +1104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>55</v>
       </c>
@@ -1104,7 +1115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>56</v>
       </c>
@@ -1115,7 +1126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>57</v>
       </c>
@@ -1128,8 +1139,11 @@
       <c r="D58" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>58</v>
       </c>
@@ -1140,7 +1154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>59</v>
       </c>
@@ -1151,7 +1165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>60</v>
       </c>
@@ -1162,7 +1176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>61</v>
       </c>
@@ -1173,7 +1187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>62</v>
       </c>
@@ -1184,7 +1198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>63</v>
       </c>
@@ -1195,7 +1209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>64</v>
       </c>
@@ -1206,7 +1220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>65</v>
       </c>
@@ -1219,8 +1233,11 @@
       <c r="D66" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>66</v>
       </c>
@@ -1231,7 +1248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>67</v>
       </c>
@@ -1242,7 +1259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>68</v>
       </c>
@@ -1253,7 +1270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>69</v>
       </c>
@@ -1264,7 +1281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>70</v>
       </c>
@@ -1275,7 +1292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>71</v>
       </c>
@@ -1286,7 +1303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>72</v>
       </c>
@@ -1297,7 +1314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>73</v>
       </c>
@@ -1308,7 +1325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>74</v>
       </c>
@@ -1319,7 +1336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>75</v>
       </c>
@@ -1330,7 +1347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>76</v>
       </c>
@@ -1341,7 +1358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>77</v>
       </c>
@@ -1354,8 +1371,11 @@
       <c r="D78" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>78</v>
       </c>
@@ -1366,7 +1386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>79</v>
       </c>
@@ -1377,7 +1397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>80</v>
       </c>
@@ -1388,7 +1408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>81</v>
       </c>
@@ -1399,7 +1419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>82</v>
       </c>
@@ -1410,7 +1430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>83</v>
       </c>
@@ -1421,7 +1441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>84</v>
       </c>
@@ -1432,7 +1452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>85</v>
       </c>
@@ -1442,8 +1462,11 @@
       <c r="C86">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>86</v>
       </c>
@@ -1454,7 +1477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>87</v>
       </c>
@@ -1465,7 +1488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>88</v>
       </c>
@@ -1476,7 +1499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>89</v>
       </c>
@@ -1487,7 +1510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>90</v>
       </c>
@@ -1498,7 +1521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>91</v>
       </c>
@@ -1509,7 +1532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>92</v>
       </c>
@@ -1520,7 +1543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>93</v>
       </c>
@@ -1533,8 +1556,11 @@
       <c r="D94" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>94</v>
       </c>
@@ -1545,7 +1571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>95</v>
       </c>
@@ -1556,7 +1582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>96</v>
       </c>
@@ -1567,7 +1593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>97</v>
       </c>
@@ -1578,7 +1604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>98</v>
       </c>
@@ -1589,7 +1615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>99</v>
       </c>
@@ -1600,7 +1626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>100</v>
       </c>
@@ -1611,7 +1637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>101</v>
       </c>
@@ -1621,8 +1647,11 @@
       <c r="C102">
         <v>0</v>
       </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E102" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>102</v>
       </c>
@@ -1632,8 +1661,9 @@
       <c r="C103">
         <v>0</v>
       </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E103" s="1"/>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>103</v>
       </c>
@@ -1643,8 +1673,9 @@
       <c r="C104">
         <v>0</v>
       </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E104" s="1"/>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>104</v>
       </c>
@@ -1654,8 +1685,9 @@
       <c r="C105">
         <v>0</v>
       </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E105" s="1"/>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>105</v>
       </c>
@@ -1665,8 +1697,9 @@
       <c r="C106">
         <v>0</v>
       </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E106" s="1"/>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>106</v>
       </c>
@@ -1676,8 +1709,9 @@
       <c r="C107">
         <v>0</v>
       </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E107" s="1"/>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>107</v>
       </c>
@@ -1687,8 +1721,9 @@
       <c r="C108">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E108" s="1"/>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>108</v>
       </c>
@@ -1698,8 +1733,9 @@
       <c r="C109">
         <v>1</v>
       </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E109" s="1"/>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>109</v>
       </c>
@@ -1712,8 +1748,11 @@
       <c r="D110" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E110" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>110</v>
       </c>
@@ -1723,8 +1762,9 @@
       <c r="C111">
         <v>0</v>
       </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E111" s="1"/>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>111</v>
       </c>
@@ -1734,8 +1774,9 @@
       <c r="C112">
         <v>0</v>
       </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E112" s="1"/>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>112</v>
       </c>
@@ -1745,8 +1786,9 @@
       <c r="C113">
         <v>0</v>
       </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E113" s="1"/>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>113</v>
       </c>
@@ -1756,8 +1798,9 @@
       <c r="C114">
         <v>0</v>
       </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E114" s="1"/>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>114</v>
       </c>
@@ -1767,8 +1810,9 @@
       <c r="C115">
         <v>0</v>
       </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E115" s="1"/>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>115</v>
       </c>
@@ -1778,8 +1822,9 @@
       <c r="C116">
         <v>0</v>
       </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E116" s="1"/>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>116</v>
       </c>
@@ -1789,8 +1834,9 @@
       <c r="C117">
         <v>0</v>
       </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E117" s="1"/>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>117</v>
       </c>
@@ -1800,8 +1846,11 @@
       <c r="C118">
         <v>0</v>
       </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E118" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>118</v>
       </c>
@@ -1811,8 +1860,9 @@
       <c r="C119">
         <v>0</v>
       </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E119" s="1"/>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>119</v>
       </c>
@@ -1822,8 +1872,9 @@
       <c r="C120">
         <v>0</v>
       </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E120" s="1"/>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>120</v>
       </c>
@@ -1833,8 +1884,9 @@
       <c r="C121">
         <v>0</v>
       </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E121" s="1"/>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>121</v>
       </c>
@@ -1844,8 +1896,9 @@
       <c r="C122">
         <v>0</v>
       </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E122" s="1"/>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>122</v>
       </c>
@@ -1855,8 +1908,9 @@
       <c r="C123">
         <v>0</v>
       </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E123" s="1"/>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>123</v>
       </c>
@@ -1866,8 +1920,9 @@
       <c r="C124">
         <v>0</v>
       </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E124" s="1"/>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>124</v>
       </c>
@@ -1877,8 +1932,9 @@
       <c r="C125">
         <v>0</v>
       </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E125" s="1"/>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>125</v>
       </c>
@@ -1891,8 +1947,11 @@
       <c r="D126" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E126" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>126</v>
       </c>
@@ -1903,7 +1962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>127</v>
       </c>
